--- a/data/trans_dic/P71_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,29; 33,17</t>
+          <t>26,94; 32,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,64; 43,98</t>
+          <t>37,34; 43,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,05; 50,95</t>
+          <t>44,13; 51,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 30,65</t>
+          <t>23,28; 30,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,61; 42,74</t>
+          <t>37,58; 43,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,61; 39,04</t>
+          <t>33,82; 38,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,27; 53,04</t>
+          <t>46,62; 52,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,73; 30,24</t>
+          <t>24,88; 30,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,6; 37,64</t>
+          <t>33,64; 37,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,19; 40,31</t>
+          <t>35,96; 40,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,55; 51,32</t>
+          <t>46,38; 51,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,91; 29,23</t>
+          <t>24,97; 29,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 16,43</t>
+          <t>12,79; 16,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,97; 32,28</t>
+          <t>28,05; 32,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,3; 36,52</t>
+          <t>32,05; 36,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 13,76</t>
+          <t>7,9; 13,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,54; 24,81</t>
+          <t>20,36; 24,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,17; 34,74</t>
+          <t>30,08; 34,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,55; 36,88</t>
+          <t>32,73; 36,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 25,75</t>
+          <t>12,94; 26,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 19,71</t>
+          <t>17,08; 19,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,5; 32,64</t>
+          <t>29,68; 32,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,02; 36,15</t>
+          <t>32,89; 36,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 18,08</t>
+          <t>11,65; 19,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,62</t>
+          <t>4,94; 9,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 15,82</t>
+          <t>9,41; 15,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 14,02</t>
+          <t>8,26; 13,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,46</t>
+          <t>1,54; 4,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 15,72</t>
+          <t>9,09; 15,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 18,38</t>
+          <t>11,65; 18,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,27</t>
+          <t>11,12; 17,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,16</t>
+          <t>3,92; 7,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,35</t>
+          <t>7,41; 11,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 16,09</t>
+          <t>11,19; 16,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,46; 14,53</t>
+          <t>10,6; 14,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,16</t>
+          <t>3,0; 5,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 19,4</t>
+          <t>16,8; 19,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,01; 32,27</t>
+          <t>29,1; 32,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,73; 35,07</t>
+          <t>31,7; 35,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 13,64</t>
+          <t>9,29; 13,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,34; 29,49</t>
+          <t>26,36; 29,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,03; 33,19</t>
+          <t>30,03; 33,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,15; 37,56</t>
+          <t>34,07; 37,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 23,09</t>
+          <t>14,38; 22,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,85; 23,98</t>
+          <t>22,05; 24,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,97; 32,29</t>
+          <t>30,0; 32,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,47; 35,79</t>
+          <t>33,4; 35,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 17,48</t>
+          <t>12,73; 17,26</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>275674; 335133</t>
+          <t>272195; 333262</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>364392; 425762</t>
+          <t>361493; 424807</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>329165; 380755</t>
+          <t>329806; 384303</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118016; 154657</t>
+          <t>117461; 154640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>482695; 548500</t>
+          <t>482314; 552293</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>447135; 519306</t>
+          <t>449906; 517913</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>457343; 524259</t>
+          <t>460805; 523781</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>183743; 224709</t>
+          <t>184883; 223749</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>770595; 863394</t>
+          <t>771554; 862116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>831869; 926416</t>
+          <t>826598; 923018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>808052; 890837</t>
+          <t>805045; 890663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>310738; 364734</t>
+          <t>311551; 366728</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>371002</t>
+          <t>371003</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>217490; 274993</t>
+          <t>214094; 272942</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>547948; 632296</t>
+          <t>549366; 631463</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>664721; 751674</t>
+          <t>659751; 751421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>188045; 311332</t>
+          <t>178814; 311258</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>320751; 387494</t>
+          <t>318012; 385215</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>528110; 608084</t>
+          <t>526491; 610175</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>643680; 729360</t>
+          <t>647347; 731035</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>287690; 564842</t>
+          <t>283945; 577725</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>549446; 637779</t>
+          <t>552637; 644890</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1094335; 1210694</t>
+          <t>1100815; 1215731</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1332757; 1458875</t>
+          <t>1327479; 1459300</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>519129; 805441</t>
+          <t>518905; 852269</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26995; 52582</t>
+          <t>27003; 51938</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43409; 75176</t>
+          <t>44713; 74502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44663; 76382</t>
+          <t>44998; 76176</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10389; 28678</t>
+          <t>9928; 29286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43939; 73811</t>
+          <t>42708; 72687</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53107; 84120</t>
+          <t>53327; 84871</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62077; 94666</t>
+          <t>60957; 93692</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24462; 46587</t>
+          <t>25511; 45616</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76028; 115360</t>
+          <t>75279; 116377</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105166; 150104</t>
+          <t>104439; 149917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114286; 158863</t>
+          <t>115871; 159996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39188; 66830</t>
+          <t>38771; 65834</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>536405; 626782</t>
+          <t>542936; 627470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>986910; 1097969</t>
+          <t>990155; 1104671</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1063194; 1175195</t>
+          <t>1062183; 1172666</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>319913; 465238</t>
+          <t>316599; 465255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>873035; 977713</t>
+          <t>873730; 977973</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1062526; 1174305</t>
+          <t>1062824; 1180451</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1200047; 1319981</t>
+          <t>1197515; 1313839</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>515613; 828571</t>
+          <t>515803; 822901</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1429935; 1569869</t>
+          <t>1443179; 1577379</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2080255; 2241161</t>
+          <t>2081987; 2236096</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2297526; 2456657</t>
+          <t>2292824; 2451188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>894882; 1223001</t>
+          <t>890887; 1208023</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P71_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,94; 32,99</t>
+          <t>27,08; 32,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,34; 43,88</t>
+          <t>37,92; 44,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,13; 51,43</t>
+          <t>43,65; 50,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,28; 30,64</t>
+          <t>25,29; 32,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,58; 43,03</t>
+          <t>37,55; 42,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,82; 38,93</t>
+          <t>33,72; 39,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,62; 52,99</t>
+          <t>46,46; 52,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,88; 30,11</t>
+          <t>25,53; 30,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,64; 37,59</t>
+          <t>33,81; 37,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,96; 40,16</t>
+          <t>35,93; 40,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,38; 51,31</t>
+          <t>46,26; 51,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,97; 29,39</t>
+          <t>26,39; 30,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 16,31</t>
+          <t>12,95; 16,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,05; 32,24</t>
+          <t>28,01; 32,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,05; 36,51</t>
+          <t>32,05; 36,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 13,76</t>
+          <t>12,6; 16,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 24,66</t>
+          <t>20,35; 24,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,08; 34,86</t>
+          <t>30,21; 34,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,73; 36,96</t>
+          <t>32,59; 36,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,94; 26,34</t>
+          <t>15,02; 18,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 19,93</t>
+          <t>17,07; 19,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,68; 32,77</t>
+          <t>29,67; 32,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 36,16</t>
+          <t>32,91; 36,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 19,13</t>
+          <t>14,28; 16,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,5</t>
+          <t>4,76; 9,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 15,68</t>
+          <t>9,33; 15,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,98</t>
+          <t>8,28; 13,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,56</t>
+          <t>1,93; 5,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 15,48</t>
+          <t>9,19; 15,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,65; 18,54</t>
+          <t>11,4; 18,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,12; 17,09</t>
+          <t>11,12; 17,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,01</t>
+          <t>4,22; 7,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 11,45</t>
+          <t>7,52; 11,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,07</t>
+          <t>11,18; 15,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,64</t>
+          <t>10,56; 14,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,09</t>
+          <t>3,47; 5,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,8; 19,42</t>
+          <t>16,71; 19,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,1; 32,47</t>
+          <t>28,9; 32,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,7; 35,0</t>
+          <t>31,67; 35,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,65</t>
+          <t>12,98; 15,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,36; 29,5</t>
+          <t>26,32; 29,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,03; 33,36</t>
+          <t>30,02; 33,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,07; 37,38</t>
+          <t>34,19; 37,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 22,94</t>
+          <t>15,74; 17,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,05; 24,1</t>
+          <t>22,0; 24,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,0; 32,22</t>
+          <t>29,91; 32,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,4; 35,71</t>
+          <t>33,45; 35,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 17,26</t>
+          <t>14,81; 16,52</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135238</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>202715</t>
+          <t>227045</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>337953</t>
+          <t>390332</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>272195; 333262</t>
+          <t>273614; 331729</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>361493; 424807</t>
+          <t>367062; 427636</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>329806; 384303</t>
+          <t>326161; 380249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117461; 154640</t>
+          <t>143102; 185261</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>482314; 552293</t>
+          <t>481911; 549111</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>449906; 517913</t>
+          <t>448609; 519944</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>460805; 523781</t>
+          <t>459205; 523435</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>184883; 223749</t>
+          <t>206853; 247830</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>771554; 862116</t>
+          <t>775483; 867180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>826598; 923018</t>
+          <t>825877; 923846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>805045; 890663</t>
+          <t>803009; 885203</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>311551; 366728</t>
+          <t>363148; 419549</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262032</t>
+          <t>313193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>371003</t>
+          <t>354800</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>633035</t>
+          <t>667993</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>214094; 272942</t>
+          <t>216808; 276715</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>549366; 631463</t>
+          <t>548709; 633015</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>659751; 751421</t>
+          <t>659628; 751159</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>178814; 311258</t>
+          <t>277160; 352160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>318012; 385215</t>
+          <t>317829; 385099</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>526491; 610175</t>
+          <t>528772; 611839</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>647347; 731035</t>
+          <t>644519; 729920</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>283945; 577725</t>
+          <t>324064; 394914</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>552637; 644890</t>
+          <t>552467; 640793</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1100815; 1215731</t>
+          <t>1100754; 1214092</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1327479; 1459300</t>
+          <t>1328114; 1452873</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>518905; 852269</t>
+          <t>622083; 722187</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>63995</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27003; 51938</t>
+          <t>26020; 51243</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44713; 74502</t>
+          <t>44343; 74713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44998; 76176</t>
+          <t>45120; 74402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9928; 29286</t>
+          <t>13656; 36574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42708; 72687</t>
+          <t>43181; 73259</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53327; 84871</t>
+          <t>52177; 85401</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60957; 93692</t>
+          <t>60941; 94128</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25511; 45616</t>
+          <t>30519; 55494</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75279; 116377</t>
+          <t>76385; 115926</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104439; 149917</t>
+          <t>104321; 145747</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115871; 159996</t>
+          <t>115437; 159988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38771; 65834</t>
+          <t>49706; 82705</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>542936; 627470</t>
+          <t>539752; 628141</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>990155; 1104671</t>
+          <t>983184; 1096749</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1062183; 1172666</t>
+          <t>1061049; 1176044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>316599; 465255</t>
+          <t>450681; 542953</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>873730; 977973</t>
+          <t>872523; 974556</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1062824; 1180451</t>
+          <t>1062463; 1173717</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1197515; 1313839</t>
+          <t>1201388; 1321203</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>515803; 822901</t>
+          <t>581195; 661527</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1443179; 1577379</t>
+          <t>1440326; 1578494</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2081987; 2236096</t>
+          <t>2075894; 2237303</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2292824; 2451188</t>
+          <t>2296136; 2457823</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>890887; 1208023</t>
+          <t>1061168; 1183409</t>
         </is>
       </c>
     </row>
